--- a/docs/testing/generated/B-survivors.xlsx
+++ b/docs/testing/generated/B-survivors.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="StockLOG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full precision" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'StockLOG'!$A$4:$T$24</definedName>
@@ -455,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYNTHETIC ACCEPTANCE FIXTURE. AUD. Animal selection filters never clip lifetime financials. Unknown purchase cost makes P/L incomplete. Active animals show costs/revenue to date, not final realised sale. Timestamps are Unix seconds; property timezone Australia/Melbourne. Stored allocations retain 12 decimal places.</t>
+          <t>SYNTHETIC ACCEPTANCE FIXTURE. AUD. Date/attribute filters select animals; their finances always cover the full lifetime. Unknown purchase prices make P/L incomplete. Active animals show costs/revenue to date, not a final sale outcome. Export dates use your display timezone. Property timezone Australia/Melbourne. Amounts are displayed to cents with reconciliation rounding; Excel also includes full-precision values.</t>
         </is>
       </c>
     </row>
@@ -467,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"dataset": "animals", "filters": {"mob": "2", "status": "exited"}}</t>
+          <t>Animals; Mob: August; Status: exited; Attributes: current; Filters: all</t>
         </is>
       </c>
     </row>
@@ -581,7 +582,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7f582f70-51b9-4385-9bc9-33e87c6c710c</t>
+          <t>30421036-df4a-43b1-a64c-3d616b91c4cb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -616,17 +617,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -641,37 +642,37 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1600210800</t>
+          <t>16/09/2020 09:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -683,7 +684,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9240e551-be2c-445c-bcc5-5f727696c88b</t>
+          <t>66cc3ea9-9754-4d52-8f1e-c8206f37713e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,17 +719,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -743,37 +744,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1600210800</t>
+          <t>16/09/2020 09:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -785,7 +786,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c5f5afd5-48f7-4bda-90bb-abe68ef5e731</t>
+          <t>aee77072-5321-45dd-af2e-3dfdd4068c26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -820,17 +821,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -845,37 +846,37 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1600210800</t>
+          <t>16/09/2020 09:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -887,7 +888,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16921463-82e9-4ecd-badb-17bb458a8def</t>
+          <t>4b523d20-3cd2-4e55-b4e0-84352dce962e</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -922,17 +923,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -947,37 +948,37 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1600210800</t>
+          <t>16/09/2020 09:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -989,7 +990,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>621b7e6d-6938-4870-b52e-986668a20d41</t>
+          <t>941edfb9-6122-4332-8525-b81dbbc41821</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1024,17 +1025,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1049,37 +1050,37 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1600210800</t>
+          <t>16/09/2020 09:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1092,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>35282957-1d9e-48f2-836a-3fe8822c9971</t>
+          <t>7b554ca4-9e5c-4da0-997d-577b1527bedc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1126,17 +1127,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1151,37 +1152,37 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1600210800</t>
+          <t>16/09/2020 09:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9ee379a6-45c7-4dcd-ad13-c935ec2004c1</t>
+          <t>ce3d5609-c2a4-488a-be6d-f2213253083d</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1228,17 +1229,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1254,32 +1255,32 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1292,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>b1302108-800f-4478-b3f4-ccc8d7c0b5cf</t>
+          <t>14d05832-d686-4911-818f-86f26b1cf6ce</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1326,17 +1327,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1352,32 +1353,32 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1390,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6684df35-a5c1-4db5-8e74-5b338afed14b</t>
+          <t>5d5b84f0-f567-4ada-bd49-102ae164c428</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1424,17 +1425,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1450,32 +1451,32 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1488,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>c8c95730-ba3e-4371-8f8e-93af57f8851f</t>
+          <t>f26fc549-2dec-4727-a464-9261dad9650a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1522,17 +1523,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1548,32 +1549,32 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1586,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fae083c1-ef6d-4d71-917a-aeffcec54ef5</t>
+          <t>2389859b-2ec5-4d7e-a9e3-044f86de15a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1620,17 +1621,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1646,32 +1647,32 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1684,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9d7d14c9-1742-466c-b886-4c9629ea5d36</t>
+          <t>d94cea83-adcf-4fa6-8650-4cc6e36611fb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1718,17 +1719,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1744,32 +1745,32 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1782,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36285a01-ccae-4255-a9f2-9f53bd51d4d3</t>
+          <t>e50e280c-dce2-41ee-ab08-7f6118b9dd38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1816,17 +1817,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1842,32 +1843,32 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1880,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>40604479-0249-40b7-a824-a9c3d06b1298</t>
+          <t>a08eb39c-314a-4cb6-9a34-122a63f3ee5a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1914,17 +1915,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1940,32 +1941,32 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1978,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>171f8246-4f8f-45e5-869b-d1d3590e48df</t>
+          <t>f8a1bcd6-54df-4811-a4e7-36c747563d01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2012,17 +2013,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2038,32 +2039,32 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2076,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0fa4bef9-140c-466b-b096-9d716c294b6b</t>
+          <t>58e289a9-7e12-435d-a447-12ebeb04d99a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2110,17 +2111,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2136,32 +2137,32 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2174,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5765f6ae-2339-4a4c-bf44-b8a70fe23536</t>
+          <t>40828550-284a-442c-864e-d1ce5977aab9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2208,17 +2209,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2234,32 +2235,32 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2eeb9c47-0572-47b3-bc47-344553cac642</t>
+          <t>1f0cb9dc-6542-4d91-bc6b-c07115dfa221</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2306,17 +2307,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2332,32 +2333,32 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2370,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>e1760d10-0942-43c7-bf06-107f23515d49</t>
+          <t>5aaff584-2139-465a-9cd7-56fa9da53592</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2404,17 +2405,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2430,32 +2431,32 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2468,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2c7440c4-848e-411f-bf0c-eb705ed61c14</t>
+          <t>7b471e10-d907-49e2-82d4-233e099f5b7c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2502,17 +2503,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2528,32 +2529,32 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2574,4 +2575,2111 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Stored precision in AUD/quantities; no financial lifetime clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>breed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>age_weeks</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>estimated_age</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>financial_complete</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>restriction_end</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>feed</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>procedure</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TESTB00000000005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30421036-df4a-43b1-a64c-3d616b91c4cb</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000005 (current); rfid:000000000000105 (current)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1600210800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TESTB00000000006</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>66cc3ea9-9754-4d52-8f1e-c8206f37713e</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000006 (current); rfid:000000000000106 (current)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1600210800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TESTB00000000007</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aee77072-5321-45dd-af2e-3dfdd4068c26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000007 (current); rfid:000000000000107 (current)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1600210800</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TESTB00000000008</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4b523d20-3cd2-4e55-b4e0-84352dce962e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000008 (current); rfid:000000000000108 (current)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1600210800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TESTB00000000009</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>941edfb9-6122-4332-8525-b81dbbc41821</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000009 (current); rfid:000000000000109 (current)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1600210800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TESTB00000000010</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7b554ca4-9e5c-4da0-997d-577b1527bedc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000010 (current); rfid:000000000000110 (current)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1600210800</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TESTB00000000011</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ce3d5609-c2a4-488a-be6d-f2213253083d</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000011 (current); rfid:000000000000111 (current)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TESTB00000000012</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14d05832-d686-4911-818f-86f26b1cf6ce</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000012 (current); rfid:000000000000112 (current)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TESTB00000000013</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5d5b84f0-f567-4ada-bd49-102ae164c428</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000013 (current); rfid:000000000000113 (current)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TESTB00000000014</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>f26fc549-2dec-4727-a464-9261dad9650a</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000014 (current); rfid:000000000000114 (current)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TESTB00000000015</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2389859b-2ec5-4d7e-a9e3-044f86de15a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000015 (current); rfid:000000000000115 (current)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TESTB00000000016</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>d94cea83-adcf-4fa6-8650-4cc6e36611fb</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000016 (current); rfid:000000000000116 (current)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TESTB00000000017</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>e50e280c-dce2-41ee-ab08-7f6118b9dd38</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000017 (current); rfid:000000000000117 (current)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TESTB00000000018</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>a08eb39c-314a-4cb6-9a34-122a63f3ee5a</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000018 (current); rfid:000000000000118 (current)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TESTB00000000019</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>f8a1bcd6-54df-4811-a4e7-36c747563d01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000019 (current); rfid:000000000000119 (current)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TESTB00000000020</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>58e289a9-7e12-435d-a447-12ebeb04d99a</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000020 (current); rfid:000000000000120 (current)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TESTB00000000021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>40828550-284a-442c-864e-d1ce5977aab9</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000021 (current); rfid:000000000000121 (current)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TESTB00000000022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1f0cb9dc-6542-4d91-bc6b-c07115dfa221</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000022 (current); rfid:000000000000122 (current)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TESTB00000000023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5aaff584-2139-465a-9cd7-56fa9da53592</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000023 (current); rfid:000000000000123 (current)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TESTB00000000024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7b471e10-d907-49e2-82d4-233e099f5b7c</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>nlis:TESTB00000000024 (current); rfid:000000000000124 (current)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>